--- a/Proyectos Modelo/Proyecto_Carretera/PRM_ProctorModificado.xlsx
+++ b/Proyectos Modelo/Proyecto_Carretera/PRM_ProctorModificado.xlsx
@@ -433,7 +433,7 @@
         <v>Volumen del molde (cm³)</v>
       </c>
       <c r="E2" t="str">
-        <v>numerico-[943:2124]:dec[1]:ej[2124]</v>
+        <v>numerico-[943:2124]:dec[1]:ej[2124]:oblig</v>
       </c>
       <c r="F2" t="str">
         <v>Datos del molde y la muestra</v>
@@ -453,7 +453,7 @@
         <v>Peso del molde vacío (g)</v>
       </c>
       <c r="E3" t="str">
-        <v>numerico-[2500:6500]:dec[1]:ej[5350]</v>
+        <v>numerico-[2500:6500]:dec[1]:ej[5350]:oblig</v>
       </c>
       <c r="F3" t="str">
         <v>Datos del molde y la muestra</v>
@@ -493,7 +493,7 @@
         <v>Peso molde + suelo húmedo (g)</v>
       </c>
       <c r="E5" t="str">
-        <v>numerico-[4500:11500]:dec[1]:ej[10260.7] // numerico-[4500:11500]:dec[1]:ej[10362.6] // numerico-[4500:11500]:dec[1]:ej[10364.8] // numerico-[4500:11500]:dec[1]:ej[10307.4]</v>
+        <v>numerico-[4500:11500]:dec[1]:ej[10260.7]:oblig // numerico-[4500:11500]:dec[1]:ej[10362.6]:oblig // numerico-[4500:11500]:dec[1]:ej[10364.8]:oblig // numerico-[4500:11500]:dec[1]:ej[10307.4]:oblig</v>
       </c>
       <c r="F5" t="str">
         <v>Determinación de la curva de compactación (4 puntos)</v>
@@ -513,7 +513,7 @@
         <v>Peso de la tara (g)</v>
       </c>
       <c r="E6" t="str">
-        <v>numerico-[15:100]:dec[2]:ej[25] // numerico-[15:100]:dec[2]:ej[25] // numerico-[15:100]:dec[2]:ej[25] // numerico-[15:100]:dec[2]:ej[25]</v>
+        <v>numerico-[15:100]:dec[2]:ej[25]:oblig // numerico-[15:100]:dec[2]:ej[25]:oblig // numerico-[15:100]:dec[2]:ej[25]:oblig // numerico-[15:100]:dec[2]:ej[25]:oblig</v>
       </c>
       <c r="F6" t="str">
         <v>Determinación de la curva de compactación (4 puntos)</v>
@@ -533,7 +533,7 @@
         <v>Peso tara + suelo húmedo (g)</v>
       </c>
       <c r="E7" t="str">
-        <v>numerico-[100:500]:dec[2]:ej[151.96] // numerico-[100:500]:dec[2]:ej[153.16] // numerico-[100:500]:dec[2]:ej[154.36] // numerico-[100:500]:dec[2]:ej[155.56]</v>
+        <v>numerico-[100:500]:dec[2]:ej[151.96]:oblig // numerico-[100:500]:dec[2]:ej[153.16]:oblig // numerico-[100:500]:dec[2]:ej[154.36]:oblig // numerico-[100:500]:dec[2]:ej[155.56]:oblig</v>
       </c>
       <c r="F7" t="str">
         <v>Determinación de la curva de compactación (4 puntos)</v>
@@ -553,7 +553,7 @@
         <v>Peso tara + suelo seco (g)</v>
       </c>
       <c r="E8" t="str">
-        <v>numerico-[90:480]:dec[2]:ej[145] // numerico-[90:480]:dec[2]:ej[145] // numerico-[90:480]:dec[2]:ej[145] // numerico-[90:480]:dec[2]:ej[145]</v>
+        <v>numerico-[90:480]:dec[2]:ej[145]:oblig // numerico-[90:480]:dec[2]:ej[145]:oblig // numerico-[90:480]:dec[2]:ej[145]:oblig // numerico-[90:480]:dec[2]:ej[145]:oblig</v>
       </c>
       <c r="F8" t="str">
         <v>Determinación de la curva de compactación (4 puntos)</v>
